--- a/artfynd/A 47948-2023 artfynd.xlsx
+++ b/artfynd/A 47948-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 47948-2023 artfynd.xlsx
+++ b/artfynd/A 47948-2023 artfynd.xlsx
@@ -932,7 +932,7 @@
         <v>121389445</v>
       </c>
       <c r="B4" t="n">
-        <v>74712</v>
+        <v>74715</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 47948-2023 artfynd.xlsx
+++ b/artfynd/A 47948-2023 artfynd.xlsx
@@ -932,7 +932,7 @@
         <v>121389445</v>
       </c>
       <c r="B4" t="n">
-        <v>74715</v>
+        <v>74717</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 47948-2023 artfynd.xlsx
+++ b/artfynd/A 47948-2023 artfynd.xlsx
@@ -932,7 +932,7 @@
         <v>121389445</v>
       </c>
       <c r="B4" t="n">
-        <v>74717</v>
+        <v>74720</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 47948-2023 artfynd.xlsx
+++ b/artfynd/A 47948-2023 artfynd.xlsx
@@ -932,7 +932,7 @@
         <v>121389445</v>
       </c>
       <c r="B4" t="n">
-        <v>74720</v>
+        <v>74721</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 47948-2023 artfynd.xlsx
+++ b/artfynd/A 47948-2023 artfynd.xlsx
@@ -932,7 +932,7 @@
         <v>121389445</v>
       </c>
       <c r="B4" t="n">
-        <v>74721</v>
+        <v>74722</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 47948-2023 artfynd.xlsx
+++ b/artfynd/A 47948-2023 artfynd.xlsx
@@ -932,7 +932,7 @@
         <v>121389445</v>
       </c>
       <c r="B4" t="n">
-        <v>74722</v>
+        <v>74729</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
